--- a/medical_application_forms/031_patient_extensive_intake_form--medical_application_forms.xlsx
+++ b/medical_application_forms/031_patient_extensive_intake_form--medical_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>medical_history</t>
+          <t>medical_history_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Medical History</t>
+          <t>Medical History 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>allergies</t>
+          <t>allergies_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Allergies</t>
+          <t>Allergies 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>medications</t>
+          <t>medications_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Medications</t>
+          <t>Medications 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -802,7 +802,7 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -895,7 +895,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>medical_history_choices</t>
+          <t>medical_history_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>medical_history_choices</t>
+          <t>medical_history_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
